--- a/public/templates/bdd_costo_mensual.xlsx
+++ b/public/templates/bdd_costo_mensual.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\tierrasanta\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07F07613-1113-4B82-89AF-3258EE8D4004}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A52971AA-FCC7-45A3-8E8B-142412D791FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="COSTO POR CAMPO" sheetId="1" r:id="rId1"/>
     <sheet name="COSTO LABORAL PLANILLA" sheetId="3" r:id="rId2"/>
-    <sheet name="COSTO TOTAL" sheetId="2" r:id="rId3"/>
+    <sheet name="Hoja1" sheetId="5" r:id="rId3"/>
+    <sheet name="COSTO CUADRILLA BONOS" sheetId="4" r:id="rId4"/>
+    <sheet name="COSTO TOTAL" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'COSTO POR CAMPO'!$A$4:$M$4</definedName>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="63">
   <si>
     <t>Área</t>
   </si>
@@ -160,6 +162,60 @@
   </si>
   <si>
     <t>BONO PRODUCTIVIDAD</t>
+  </si>
+  <si>
+    <t>SERVICIOS CAMPOS</t>
+  </si>
+  <si>
+    <t>REPORTE DE COSTOS DE BONOS DE CUADRILLA</t>
+  </si>
+  <si>
+    <t>Resumen de bonos por fecha</t>
+  </si>
+  <si>
+    <t>COSTO TOTAL CUADRILLA</t>
+  </si>
+  <si>
+    <t>TOTAL CUADRILLEROS</t>
+  </si>
+  <si>
+    <t>ENERO 2026</t>
+  </si>
+  <si>
+    <t>28/09/2026 15:48:27</t>
+  </si>
+  <si>
+    <t>CUADRILLERO</t>
+  </si>
+  <si>
+    <t>LABOR</t>
+  </si>
+  <si>
+    <t>METODO</t>
+  </si>
+  <si>
+    <t>CUADRILLA BONO PRODUCTIVIDAD</t>
+  </si>
+  <si>
+    <t>TOTAL KG</t>
+  </si>
+  <si>
+    <t>REPORTE DE COSTOS DE CUADRILLA</t>
+  </si>
+  <si>
+    <t>Resumen de costos por fecha</t>
+  </si>
+  <si>
+    <t>28/09/2026 16:31:52</t>
+  </si>
+  <si>
+    <t>JORNAL</t>
+  </si>
+  <si>
+    <t>BONO</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
   </si>
 </sst>
 </file>
@@ -170,7 +226,7 @@
     <numFmt numFmtId="44" formatCode="_-&quot;S/&quot;\ * #,##0.00_-;\-&quot;S/&quot;\ * #,##0.00_-;_-&quot;S/&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -250,8 +306,35 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1F4E86"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF1F4E86"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -300,8 +383,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E86"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDF3F9"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -440,12 +535,100 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF8EA9DB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF8EA9DB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF8EA9DB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF8EA9DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF8EA9DB"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF8EA9DB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF8EA9DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -562,6 +745,43 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="14" fillId="10" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="15" fillId="10" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="6" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -636,21 +856,182 @@
     <xf numFmtId="4" fontId="10" fillId="8" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="13" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="14" fillId="10" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="14" fillId="10" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="15" fillId="10" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="17" fontId="15" fillId="10" borderId="19" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="15" fillId="10" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="15" fillId="10" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="26">
+  <dxfs count="31">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;S/&quot;\ * #,##0.00_-;\-&quot;S/&quot;\ * #,##0.00_-;_-&quot;S/&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;S/&quot;\ * #,##0.00_-;\-&quot;S/&quot;\ * #,##0.00_-;_-&quot;S/&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -668,13 +1049,24 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -702,91 +1094,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;S/&quot;\ * #,##0.00_-;\-&quot;S/&quot;\ * #,##0.00_-;_-&quot;S/&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;S/&quot;\ * #,##0.00_-;\-&quot;S/&quot;\ * #,##0.00_-;_-&quot;S/&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -805,24 +1116,10 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -916,37 +1213,171 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>213360</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>281940</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46C752EC-0E9F-4A11-8322-E91E7F0D09D5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="66675" y="152400"/>
+          <a:ext cx="542925" cy="518160"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>487680</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>342900</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBD43DA8-CC2E-490A-B5AA-493DD0F814C1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="66675" y="152400"/>
+          <a:ext cx="817245" cy="579120"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{275C6DC4-33E2-4EB2-B71A-B63A2C67D21D}" name="tblCostoPlanillaMensual" displayName="tblCostoPlanillaMensual" ref="A7:G8" insertRow="1" totalsRowShown="0" headerRowDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{275C6DC4-33E2-4EB2-B71A-B63A2C67D21D}" name="tblCostoPlanillaMensual" displayName="tblCostoPlanillaMensual" ref="A7:G8" insertRow="1" totalsRowShown="0" headerRowDxfId="30">
   <autoFilter ref="A7:G8" xr:uid="{275C6DC4-33E2-4EB2-B71A-B63A2C67D21D}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{C159FE92-5B01-449F-AE71-631BD254E04E}" name="N°" dataDxfId="24"/>
+    <tableColumn id="1" xr3:uid="{C159FE92-5B01-449F-AE71-631BD254E04E}" name="N°" dataDxfId="29"/>
     <tableColumn id="2" xr3:uid="{9B89B643-F63A-4A0F-AE6A-F929AFBC4D17}" name="NOMBRE EMPLEADO"/>
-    <tableColumn id="3" xr3:uid="{8DF0E71C-85BD-40A6-ABCB-35E28C3BD8FC}" name="SUELDO PAGADO" dataDxfId="23" dataCellStyle="Moneda"/>
-    <tableColumn id="4" xr3:uid="{B8FBA746-56FE-4F19-8E41-2ED4542BF715}" name="APORTES DEL TRABAJADOR" dataDxfId="22" dataCellStyle="Moneda"/>
-    <tableColumn id="5" xr3:uid="{5412C88C-65A9-4EE3-881F-5A88455AEA6F}" name="APORTES DEL EMPLEADOR" dataDxfId="1" dataCellStyle="Moneda"/>
-    <tableColumn id="7" xr3:uid="{B7B7AFD8-71E1-457D-8557-B2A6A4E3A9D2}" name="BONO PRODUCTIVIDAD" dataDxfId="0" dataCellStyle="Moneda"/>
-    <tableColumn id="6" xr3:uid="{453B62C9-7CEA-4FE5-AA62-8A3BEE898C21}" name="COSTO TOTAL EMPRESA" dataDxfId="2" dataCellStyle="Moneda"/>
+    <tableColumn id="3" xr3:uid="{8DF0E71C-85BD-40A6-ABCB-35E28C3BD8FC}" name="SUELDO PAGADO" dataDxfId="28" dataCellStyle="Moneda"/>
+    <tableColumn id="4" xr3:uid="{B8FBA746-56FE-4F19-8E41-2ED4542BF715}" name="APORTES DEL TRABAJADOR" dataDxfId="27" dataCellStyle="Moneda"/>
+    <tableColumn id="5" xr3:uid="{5412C88C-65A9-4EE3-881F-5A88455AEA6F}" name="APORTES DEL EMPLEADOR" dataDxfId="26" dataCellStyle="Moneda"/>
+    <tableColumn id="7" xr3:uid="{B7B7AFD8-71E1-457D-8557-B2A6A4E3A9D2}" name="BONO PRODUCTIVIDAD" dataDxfId="25" dataCellStyle="Moneda"/>
+    <tableColumn id="6" xr3:uid="{453B62C9-7CEA-4FE5-AA62-8A3BEE898C21}" name="COSTO TOTAL EMPRESA" dataDxfId="24" dataCellStyle="Moneda"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F06A4B39-294C-420F-97C4-E54FE34E21EC}" name="Tabla2" displayName="Tabla2" ref="A4:I7" headerRowDxfId="3">
-  <autoFilter ref="A4:I7" xr:uid="{F06A4B39-294C-420F-97C4-E54FE34E21EC}"/>
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C169548E-2272-4DFD-81C3-AA1D5F6B7327}" name="tblCostoCuadrilla" displayName="tblCostoCuadrilla" ref="A7:H8" insertRow="1">
+  <autoFilter ref="A7:H8" xr:uid="{C169548E-2272-4DFD-81C3-AA1D5F6B7327}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{941AB5DF-2531-4EBB-8BE9-0924867B6688}" name="N°"/>
+    <tableColumn id="2" xr3:uid="{EAE5B27F-D828-4E5D-B5A5-9D19483A3E4D}" name="FECHA"/>
+    <tableColumn id="3" xr3:uid="{C0B1C413-4D50-48FB-BCE6-5FC028DF4B90}" name="CUADRILLERO"/>
+    <tableColumn id="4" xr3:uid="{3D3E6C2C-9954-45F5-AEEB-61B76C56EE38}" name="CAMPO"/>
+    <tableColumn id="5" xr3:uid="{503704B3-D73A-4252-B221-C4F17240AE91}" name="LABOR"/>
+    <tableColumn id="6" xr3:uid="{90548D49-8B0B-43E3-839B-1559A9E9B468}" name="JORNAL"/>
+    <tableColumn id="7" xr3:uid="{4B711389-7719-42D6-8B59-0E5FDA35A781}" name="BONO"/>
+    <tableColumn id="8" xr3:uid="{FF0F3899-D9DC-47CB-A26C-177AD5C2BF18}" name="TOTAL"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9805C90E-CA7D-4362-AB19-C5371CCA5DC0}" name="tblBonoCuadrilla" displayName="tblBonoCuadrilla" ref="A7:H8" insertRow="1">
+  <autoFilter ref="A7:H8" xr:uid="{9805C90E-CA7D-4362-AB19-C5371CCA5DC0}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{F9F46190-2300-434F-9FBB-21D09CA806A4}" name="N°"/>
+    <tableColumn id="8" xr3:uid="{59F818F2-1C46-4D18-AB88-3C8EB33B61F1}" name="FECHA"/>
+    <tableColumn id="2" xr3:uid="{2EB428BA-9ECA-4B74-8DE9-C10693F7B024}" name="CUADRILLERO"/>
+    <tableColumn id="3" xr3:uid="{6609965B-E123-490E-8395-C42FF3F00989}" name="CAMPO" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{C6260467-C642-497D-AF6D-FF44A9C6CEB1}" name="LABOR"/>
+    <tableColumn id="5" xr3:uid="{76A2D74F-6938-4478-822D-C8B95DBB754C}" name="TOTAL KG"/>
+    <tableColumn id="6" xr3:uid="{FEE1EA48-1D63-435C-B316-0406547FDC58}" name="METODO"/>
+    <tableColumn id="7" xr3:uid="{CC985A8B-9528-4C39-AD70-170044FF27EB}" name="BONO PRODUCTIVIDAD"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F06A4B39-294C-420F-97C4-E54FE34E21EC}" name="Tabla2" displayName="Tabla2" ref="A4:K7" headerRowDxfId="22">
+  <autoFilter ref="A4:K7" xr:uid="{F06A4B39-294C-420F-97C4-E54FE34E21EC}"/>
+  <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{2907273D-C11E-4E1E-9EB3-02BD1CC84CA6}" name="MES" totalsRowLabel="Total" dataDxfId="21" totalsRowDxfId="20"/>
     <tableColumn id="2" xr3:uid="{9CD235A8-2235-4B0D-8DB1-99F5B4282247}" name="PLANILLA" dataDxfId="19" totalsRowDxfId="18" dataCellStyle="Moneda">
       <calculatedColumnFormula>B3-B4</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{4F0CC146-7C00-4621-932D-4F8FF6524B32}" name="PLANILLA BONO PRODUCTIVIDAD" dataDxfId="4" totalsRowDxfId="5" dataCellStyle="Moneda"/>
-    <tableColumn id="3" xr3:uid="{58D81BF4-3D56-4616-9378-B15ACCE87B7C}" name="CUADRILLA" dataDxfId="17" totalsRowDxfId="16" dataCellStyle="Moneda"/>
-    <tableColumn id="4" xr3:uid="{A02A0E9E-FDFD-42C6-AD5C-FBB28DC980FA}" name="MAQUINARIA" dataDxfId="15" totalsRowDxfId="14" dataCellStyle="Moneda"/>
-    <tableColumn id="5" xr3:uid="{C67ABD93-7F07-4989-AA06-CC63EDDBCE7D}" name="PESTICIDAS" dataDxfId="13" totalsRowDxfId="12" dataCellStyle="Moneda"/>
-    <tableColumn id="6" xr3:uid="{5509C64D-975E-4FA2-A434-70C957CCAFD9}" name="FERTILIZANTES" dataDxfId="11" totalsRowDxfId="10" dataCellStyle="Moneda"/>
-    <tableColumn id="7" xr3:uid="{ADA849BF-730B-440E-B74D-D2BED82DE221}" name="GENERALES" totalsRowFunction="count" dataDxfId="9" totalsRowDxfId="8" dataCellStyle="Moneda"/>
-    <tableColumn id="8" xr3:uid="{6750E0BA-AD48-4AA8-8A44-1D8F376B103D}" name="COSTO TOTAL" dataDxfId="7" totalsRowDxfId="6" dataCellStyle="Moneda" totalsRowCellStyle="Moneda">
+    <tableColumn id="9" xr3:uid="{4F0CC146-7C00-4621-932D-4F8FF6524B32}" name="PLANILLA BONO PRODUCTIVIDAD" dataDxfId="17" totalsRowDxfId="16" dataCellStyle="Moneda"/>
+    <tableColumn id="3" xr3:uid="{58D81BF4-3D56-4616-9378-B15ACCE87B7C}" name="CUADRILLA" dataDxfId="15" totalsRowDxfId="14" dataCellStyle="Moneda"/>
+    <tableColumn id="11" xr3:uid="{2D9D64D7-D66C-470E-BCE9-3514D8EC74CB}" name="CUADRILLA BONO PRODUCTIVIDAD" dataDxfId="13" totalsRowDxfId="12" dataCellStyle="Moneda"/>
+    <tableColumn id="4" xr3:uid="{A02A0E9E-FDFD-42C6-AD5C-FBB28DC980FA}" name="MAQUINARIA" dataDxfId="11" totalsRowDxfId="10" dataCellStyle="Moneda"/>
+    <tableColumn id="5" xr3:uid="{C67ABD93-7F07-4989-AA06-CC63EDDBCE7D}" name="PESTICIDAS" dataDxfId="9" totalsRowDxfId="8" dataCellStyle="Moneda"/>
+    <tableColumn id="6" xr3:uid="{5509C64D-975E-4FA2-A434-70C957CCAFD9}" name="FERTILIZANTES" dataDxfId="7" totalsRowDxfId="6" dataCellStyle="Moneda"/>
+    <tableColumn id="10" xr3:uid="{739BE56D-8173-44DB-A614-20BB3F63B610}" name="SERVICIOS CAMPOS" dataDxfId="5" totalsRowDxfId="4" dataCellStyle="Moneda"/>
+    <tableColumn id="7" xr3:uid="{ADA849BF-730B-440E-B74D-D2BED82DE221}" name="GENERALES" totalsRowFunction="count" dataDxfId="3" totalsRowDxfId="2" dataCellStyle="Moneda"/>
+    <tableColumn id="8" xr3:uid="{6750E0BA-AD48-4AA8-8A44-1D8F376B103D}" name="COSTO TOTAL" dataDxfId="1" totalsRowDxfId="0" dataCellStyle="Moneda" totalsRowCellStyle="Moneda">
       <calculatedColumnFormula>SUM(Tabla2[[#This Row],[PLANILLA]:[GENERALES]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1298,20 +1729,20 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
+      <c r="K1" s="58"/>
+      <c r="L1" s="58"/>
+      <c r="M1" s="58"/>
     </row>
     <row r="2" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3">
@@ -1331,43 +1762,43 @@
       <c r="M2" s="6"/>
     </row>
     <row r="3" spans="1:13" s="11" customFormat="1" ht="24.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="38" t="s">
+      <c r="C3" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="38" t="s">
+      <c r="D3" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="47" t="s">
+      <c r="E3" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="47"/>
-      <c r="G3" s="46" t="s">
+      <c r="F3" s="60"/>
+      <c r="G3" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="46"/>
-      <c r="I3" s="48" t="s">
+      <c r="H3" s="59"/>
+      <c r="I3" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="J3" s="48"/>
-      <c r="K3" s="48"/>
-      <c r="L3" s="40" t="s">
+      <c r="J3" s="61"/>
+      <c r="K3" s="61"/>
+      <c r="L3" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="M3" s="42" t="s">
+      <c r="M3" s="55" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="11" customFormat="1" ht="34.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="37"/>
-      <c r="B4" s="39"/>
-      <c r="C4" s="39"/>
-      <c r="D4" s="39"/>
+      <c r="A4" s="50"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
       <c r="E4" s="8" t="s">
         <v>14</v>
       </c>
@@ -1389,8 +1820,8 @@
       <c r="K4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="L4" s="41"/>
-      <c r="M4" s="43"/>
+      <c r="L4" s="54"/>
+      <c r="M4" s="56"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:M4" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -1422,37 +1853,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
     </row>
     <row r="2" spans="1:7" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
     </row>
     <row r="3" spans="1:7" ht="4.8" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="53"/>
-      <c r="C4" s="56" t="s">
+      <c r="B4" s="66"/>
+      <c r="C4" s="69" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="57"/>
+      <c r="D4" s="70"/>
       <c r="E4" s="31" t="s">
         <v>27</v>
       </c>
@@ -1462,13 +1893,13 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="54"/>
-      <c r="B5" s="55"/>
-      <c r="C5" s="58">
+      <c r="A5" s="67"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="71">
         <f>SUM(tblCostoPlanillaMensual[COSTO TOTAL EMPRESA])</f>
         <v>0</v>
       </c>
-      <c r="D5" s="59"/>
+      <c r="D5" s="72"/>
       <c r="E5" s="33">
         <f>COUNTA(tblCostoPlanillaMensual[N°])</f>
         <v>0</v>
@@ -1507,7 +1938,7 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F8" s="62"/>
+      <c r="F8" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1528,70 +1959,352 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80D7DC11-E62B-4982-B2AA-A01ED9829B5B}">
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="5.77734375" style="30" customWidth="1"/>
+    <col min="2" max="2" width="15.77734375" style="30" customWidth="1"/>
+    <col min="3" max="3" width="31.109375" customWidth="1"/>
+    <col min="4" max="4" width="16.88671875" style="48" customWidth="1"/>
+    <col min="5" max="5" width="46.33203125" style="39" customWidth="1"/>
+    <col min="6" max="8" width="24.5546875" style="39" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="30.6" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="73" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+    </row>
+    <row r="2" spans="1:8" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="74" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" s="74"/>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+    </row>
+    <row r="3" spans="1:8" ht="4.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H3"/>
+    </row>
+    <row r="4" spans="1:8" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="76" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="77"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="79" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="80"/>
+      <c r="F4" s="40" t="s">
+        <v>49</v>
+      </c>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="81" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="82"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="84">
+        <f>SUM(H8:H8)</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="85"/>
+      <c r="F5" s="41">
+        <v>23</v>
+      </c>
+      <c r="G5" s="41"/>
+      <c r="H5" s="42" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="4.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="43"/>
+    </row>
+    <row r="7" spans="1:8" s="27" customFormat="1" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" s="45" t="s">
+        <v>60</v>
+      </c>
+      <c r="G7" s="45" t="s">
+        <v>61</v>
+      </c>
+      <c r="H7" s="45" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D8"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="47"/>
+      <c r="H8" s="47"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:E5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42F0CADE-A992-46B8-BD2F-D84E02C021EB}">
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="5.77734375" style="30" customWidth="1"/>
+    <col min="2" max="2" width="15.77734375" style="30" customWidth="1"/>
+    <col min="3" max="3" width="31.109375" customWidth="1"/>
+    <col min="4" max="4" width="16.88671875" style="48" customWidth="1"/>
+    <col min="5" max="5" width="46.33203125" style="39" customWidth="1"/>
+    <col min="6" max="8" width="24.5546875" style="39" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="30.6" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="73" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+    </row>
+    <row r="2" spans="1:8" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="74" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="74"/>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+    </row>
+    <row r="3" spans="1:8" ht="4.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H3"/>
+    </row>
+    <row r="4" spans="1:8" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="76" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="77"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="79" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="80"/>
+      <c r="F4" s="40" t="s">
+        <v>49</v>
+      </c>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="81" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="82"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="84">
+        <v>108405.80351852</v>
+      </c>
+      <c r="E5" s="85"/>
+      <c r="F5" s="41">
+        <v>48</v>
+      </c>
+      <c r="G5" s="41"/>
+      <c r="H5" s="42" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="4.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="43"/>
+    </row>
+    <row r="7" spans="1:8" s="27" customFormat="1" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" s="45" t="s">
+        <v>56</v>
+      </c>
+      <c r="G7" s="45" t="s">
+        <v>54</v>
+      </c>
+      <c r="H7" s="45" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8"/>
+      <c r="B8"/>
+      <c r="D8"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="47"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:E5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BF17FEE-781B-4A30-8714-7E571BDE43A7}">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.6640625" customWidth="1"/>
-    <col min="2" max="9" width="20.5546875" customWidth="1"/>
+    <col min="2" max="4" width="20.5546875" customWidth="1"/>
+    <col min="5" max="5" width="22.44140625" customWidth="1"/>
+    <col min="6" max="8" width="20.5546875" customWidth="1"/>
+    <col min="9" max="9" width="23.44140625" customWidth="1"/>
+    <col min="10" max="11" width="20.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="49" t="s">
+    <row r="1" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="62" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-    </row>
-    <row r="2" spans="1:9" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="50" t="s">
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="62"/>
+    </row>
+    <row r="2" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="63" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-    </row>
-    <row r="4" spans="1:9" s="61" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="60" t="s">
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="63"/>
+    </row>
+    <row r="4" spans="1:11" s="37" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="60" t="s">
+      <c r="B4" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="60" t="s">
+      <c r="C4" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="60" t="s">
+      <c r="D4" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="60" t="s">
+      <c r="E4" s="45" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="60" t="s">
+      <c r="G4" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="60" t="s">
+      <c r="H4" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="H4" s="60" t="s">
+      <c r="I4" s="36" t="s">
+        <v>45</v>
+      </c>
+      <c r="J4" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="I4" s="60" t="s">
+      <c r="K4" s="36" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="34" t="s">
         <v>38</v>
       </c>
@@ -1602,12 +2315,14 @@
       <c r="F5" s="35"/>
       <c r="G5" s="35"/>
       <c r="H5" s="35"/>
-      <c r="I5" s="35">
+      <c r="I5" s="35"/>
+      <c r="J5" s="35"/>
+      <c r="K5" s="35">
         <f>SUM(Tabla2[[#This Row],[PLANILLA]:[GENERALES]])</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="34" t="s">
         <v>37</v>
       </c>
@@ -1618,12 +2333,14 @@
       <c r="F6" s="35"/>
       <c r="G6" s="35"/>
       <c r="H6" s="35"/>
-      <c r="I6" s="35">
+      <c r="I6" s="35"/>
+      <c r="J6" s="35"/>
+      <c r="K6" s="35">
         <f>SUM(Tabla2[[#This Row],[PLANILLA]:[GENERALES]])</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="34" t="s">
         <v>39</v>
       </c>
@@ -1639,31 +2356,33 @@
         <f t="shared" ref="D7" si="1">D5-D6</f>
         <v>0</v>
       </c>
-      <c r="E7" s="35">
-        <f t="shared" ref="E7" si="2">E5-E6</f>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35">
+        <f t="shared" ref="F7" si="2">F5-F6</f>
         <v>0</v>
       </c>
-      <c r="F7" s="35">
-        <f t="shared" ref="F7" si="3">F5-F6</f>
+      <c r="G7" s="35">
+        <f t="shared" ref="G7" si="3">G5-G6</f>
         <v>0</v>
       </c>
-      <c r="G7" s="35">
-        <f t="shared" ref="G7" si="4">G5-G6</f>
+      <c r="H7" s="35">
+        <f t="shared" ref="H7" si="4">H5-H6</f>
         <v>0</v>
       </c>
-      <c r="H7" s="35">
-        <f t="shared" ref="H7" si="5">H5-H6</f>
+      <c r="I7" s="35"/>
+      <c r="J7" s="35">
+        <f t="shared" ref="J7" si="5">J5-J6</f>
         <v>0</v>
       </c>
-      <c r="I7" s="35">
-        <f t="shared" ref="I7" si="6">I5-I6</f>
+      <c r="K7" s="35">
+        <f t="shared" ref="K7" si="6">K5-K6</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
